--- a/input/开发计划.xlsx
+++ b/input/开发计划.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="207">
   <si>
     <t>课程在此阶段培养的是训练机器人走向人类生产生活，提高效率创造价值的知识、技能、相关经验的人才：</t>
   </si>
@@ -162,16 +162,13 @@
     <t>高职、本科</t>
   </si>
   <si>
-    <t>镐京学院-刘力恺</t>
+    <t>镐京学院-刘力恺、胡嘉乐</t>
   </si>
   <si>
     <t>李奎</t>
   </si>
   <si>
     <t>7月中旬-8月中旬</t>
-  </si>
-  <si>
-    <t>⏳ 待开发</t>
   </si>
   <si>
     <t>机器人自然语言交互应用与开发</t>
@@ -185,15 +182,18 @@
     <t>机器人ROS2应用与开发</t>
   </si>
   <si>
+    <t>广州商学院-张景全、霍路远</t>
+  </si>
+  <si>
+    <t>机器人SLAM与Nav应用开发</t>
+  </si>
+  <si>
+    <t>小车C1</t>
+  </si>
+  <si>
     <t>广州商学院-张景全</t>
   </si>
   <si>
-    <t>机器人SLAM与Nav应用开发</t>
-  </si>
-  <si>
-    <t>小车C1</t>
-  </si>
-  <si>
     <t>机器人机械臂应用与开发</t>
   </si>
   <si>
@@ -206,7 +206,7 @@
     <t>机器人大模型综合应用开发</t>
   </si>
   <si>
-    <t>综合实训实践</t>
+    <t>综合实训实践-工厂</t>
   </si>
   <si>
     <t>实验箱B2</t>
@@ -218,13 +218,19 @@
     <t>6月中旬-7月中旬</t>
   </si>
   <si>
-    <t>🔄 开发中</t>
-  </si>
-  <si>
     <t>总部-李奎</t>
   </si>
   <si>
+    <t>综合实训实践-交通</t>
+  </si>
+  <si>
+    <t>总部-胡嘉乐</t>
+  </si>
+  <si>
     <t>7月中旬-8月初</t>
+  </si>
+  <si>
+    <t>⏳ 待开发</t>
   </si>
   <si>
     <t>🏭 三、行业应用场景（共4个，待确认开发计划）</t>
@@ -256,6 +262,9 @@
   </si>
   <si>
     <t>宇树机器狗Go2edu-U3</t>
+  </si>
+  <si>
+    <t>🔄 开发中</t>
   </si>
   <si>
     <t>状态说明：✅ 已完成  |  🔄 开发中  |  ⏳ 待开发  |  内容审核人：李奎  |  产物最终验收评审：马总、云总、进兵、申文、李奎</t>
@@ -3346,7 +3355,7 @@
         <v>43</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8">
@@ -3354,7 +3363,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>39</v>
@@ -3363,7 +3372,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="57" t="s">
         <v>42</v>
@@ -3372,7 +3381,7 @@
         <v>43</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8">
@@ -3380,7 +3389,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>39</v>
@@ -3389,7 +3398,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="57" t="s">
         <v>42</v>
@@ -3398,7 +3407,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8">
@@ -3406,16 +3415,16 @@
         <v>4</v>
       </c>
       <c r="B16" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="58" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>50</v>
       </c>
       <c r="D16" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F16" s="57" t="s">
         <v>42</v>
@@ -3424,7 +3433,7 @@
         <v>43</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8">
@@ -3450,7 +3459,7 @@
         <v>53</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8">
@@ -3467,7 +3476,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" s="57" t="s">
         <v>42</v>
@@ -3476,7 +3485,7 @@
         <v>43</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:8">
@@ -3502,7 +3511,7 @@
         <v>58</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:8">
@@ -3511,13 +3520,13 @@
         <v>55</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="57" t="s">
         <v>42</v>
@@ -3526,31 +3535,31 @@
         <v>58</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:8">
       <c r="A21" s="61"/>
       <c r="B21" s="58" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="57" t="s">
         <v>42</v>
       </c>
       <c r="G21" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:8">
@@ -3565,7 +3574,7 @@
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:8">
       <c r="A23" s="62" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" spans="1:8">
@@ -3588,7 +3597,7 @@
         <v>35</v>
       </c>
       <c r="G24" s="56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H24" s="56" t="s">
         <v>37</v>
@@ -3599,16 +3608,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F25" s="57" t="s">
         <v>42</v>
@@ -3617,7 +3626,7 @@
         <v>58</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1" spans="1:8">
@@ -3625,16 +3634,16 @@
         <v>9</v>
       </c>
       <c r="B26" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="58" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>65</v>
       </c>
       <c r="D26" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F26" s="57" t="s">
         <v>42</v>
@@ -3643,7 +3652,7 @@
         <v>58</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1" spans="1:8">
@@ -3651,16 +3660,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="58" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D27" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F27" s="57" t="s">
         <v>42</v>
@@ -3669,7 +3678,7 @@
         <v>58</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:8">
@@ -3677,16 +3686,16 @@
         <v>11</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D28" s="57" t="s">
         <v>40</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F28" s="57" t="s">
         <v>42</v>
@@ -3695,7 +3704,7 @@
         <v>53</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3710,7 +3719,7 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:8">
       <c r="A30" s="63" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -3760,28 +3769,28 @@
   <sheetData>
     <row r="1" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A1" s="25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="A2" s="27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D2" s="29">
         <v>4</v>
@@ -3790,10 +3799,10 @@
     <row r="3" s="23" customFormat="1" ht="46" customHeight="1" spans="1:5">
       <c r="A3" s="30"/>
       <c r="B3" s="28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" s="29">
         <v>4</v>
@@ -3803,10 +3812,10 @@
     <row r="4" s="23" customFormat="1" ht="33" customHeight="1" spans="1:5">
       <c r="A4" s="30"/>
       <c r="B4" s="28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D4" s="29">
         <v>4</v>
@@ -3816,10 +3825,10 @@
     <row r="5" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A5" s="30"/>
       <c r="B5" s="28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D5" s="29">
         <v>4</v>
@@ -3828,10 +3837,10 @@
     <row r="6" s="23" customFormat="1" ht="67.5" customHeight="1" spans="1:5">
       <c r="A6" s="30"/>
       <c r="B6" s="28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D6" s="29">
         <v>4</v>
@@ -3840,10 +3849,10 @@
     <row r="7" s="23" customFormat="1" ht="91" customHeight="1" spans="1:5">
       <c r="A7" s="30"/>
       <c r="B7" s="28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" s="29">
         <v>4</v>
@@ -3853,10 +3862,10 @@
     <row r="8" s="23" customFormat="1" ht="27" customHeight="1" spans="1:5">
       <c r="A8" s="30"/>
       <c r="B8" s="28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D8" s="29">
         <v>4</v>
@@ -3866,10 +3875,10 @@
     <row r="9" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="A9" s="30"/>
       <c r="B9" s="28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" s="29">
         <v>4</v>
@@ -3878,10 +3887,10 @@
     <row r="10" s="23" customFormat="1" ht="27" customHeight="1" spans="1:5">
       <c r="A10" s="30"/>
       <c r="B10" s="28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D10" s="29">
         <v>4</v>
@@ -3891,10 +3900,10 @@
     <row r="11" s="23" customFormat="1" ht="27" customHeight="1" spans="1:5">
       <c r="A11" s="30"/>
       <c r="B11" s="28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" s="29">
         <v>4</v>
@@ -3904,10 +3913,10 @@
     <row r="12" s="23" customFormat="1" ht="27" customHeight="1" spans="1:5">
       <c r="A12" s="30"/>
       <c r="B12" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D12" s="29">
         <v>4</v>
@@ -3917,10 +3926,10 @@
     <row r="13" s="23" customFormat="1" ht="27" customHeight="1" spans="1:5">
       <c r="A13" s="35"/>
       <c r="B13" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D13" s="29">
         <v>4</v>
@@ -3929,7 +3938,7 @@
     </row>
     <row r="14" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A14" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" s="37"/>
       <c r="C14" s="38"/>
@@ -3940,77 +3949,77 @@
     </row>
     <row r="15" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="A15" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="B16" s="28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="B17" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="29" t="s">
         <v>108</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="B18" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="B19" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" s="23" customFormat="1" ht="45" customHeight="1" spans="1:5">
       <c r="B20" s="28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E20"/>
     </row>
     <row r="21" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A21" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B21" s="37"/>
       <c r="C21" s="38"/>
@@ -4021,13 +4030,13 @@
     </row>
     <row r="22" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A22" s="27" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D22" s="29">
         <v>8</v>
@@ -4036,10 +4045,10 @@
     <row r="23" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A23" s="30"/>
       <c r="B23" s="28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D23" s="29">
         <v>8</v>
@@ -4048,10 +4057,10 @@
     <row r="24" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="A24" s="30"/>
       <c r="B24" s="28" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D24" s="29">
         <v>8</v>
@@ -4060,10 +4069,10 @@
     <row r="25" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A25" s="30"/>
       <c r="B25" s="28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D25" s="29">
         <v>4</v>
@@ -4072,10 +4081,10 @@
     <row r="26" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A26" s="30"/>
       <c r="B26" s="28" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D26" s="29">
         <v>6</v>
@@ -4084,10 +4093,10 @@
     <row r="27" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A27" s="30"/>
       <c r="B27" s="28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D27" s="29">
         <v>4</v>
@@ -4096,10 +4105,10 @@
     <row r="28" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A28" s="30"/>
       <c r="B28" s="28" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D28" s="29">
         <v>6</v>
@@ -4108,10 +4117,10 @@
     <row r="29" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A29" s="35"/>
       <c r="B29" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D29" s="29">
         <v>4</v>
@@ -4119,7 +4128,7 @@
     </row>
     <row r="30" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A30" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B30" s="37"/>
       <c r="C30" s="38"/>
@@ -4129,13 +4138,13 @@
     </row>
     <row r="31" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:5">
       <c r="A31" s="27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D31" s="29">
         <v>4</v>
@@ -4144,10 +4153,10 @@
     <row r="32" s="23" customFormat="1" ht="54" customHeight="1" spans="1:5">
       <c r="A32" s="30"/>
       <c r="B32" s="28" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D32" s="29">
         <v>4</v>
@@ -4156,10 +4165,10 @@
     <row r="33" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A33" s="30"/>
       <c r="B33" s="28" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D33" s="29">
         <v>8</v>
@@ -4168,10 +4177,10 @@
     <row r="34" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A34" s="30"/>
       <c r="B34" s="28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D34" s="29">
         <v>8</v>
@@ -4180,10 +4189,10 @@
     <row r="35" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A35" s="30"/>
       <c r="B35" s="28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D35" s="29">
         <v>8</v>
@@ -4192,10 +4201,10 @@
     <row r="36" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A36" s="30"/>
       <c r="B36" s="28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D36" s="29">
         <v>8</v>
@@ -4204,10 +4213,10 @@
     <row r="37" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A37" s="35"/>
       <c r="B37" s="28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D37" s="29">
         <v>8</v>
@@ -4215,7 +4224,7 @@
     </row>
     <row r="38" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A38" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B38" s="37"/>
       <c r="C38" s="38"/>
@@ -4225,13 +4234,13 @@
     </row>
     <row r="39" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A39" s="27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D39" s="29">
         <v>4</v>
@@ -4240,10 +4249,10 @@
     <row r="40" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A40" s="30"/>
       <c r="B40" s="28" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D40" s="29">
         <v>4</v>
@@ -4252,10 +4261,10 @@
     <row r="41" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A41" s="30"/>
       <c r="B41" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D41" s="29">
         <v>4</v>
@@ -4264,10 +4273,10 @@
     <row r="42" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A42" s="30"/>
       <c r="B42" s="28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D42" s="29">
         <v>4</v>
@@ -4276,10 +4285,10 @@
     <row r="43" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A43" s="30"/>
       <c r="B43" s="28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D43" s="29">
         <v>4</v>
@@ -4288,10 +4297,10 @@
     <row r="44" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A44" s="30"/>
       <c r="B44" s="28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D44" s="29">
         <v>4</v>
@@ -4300,10 +4309,10 @@
     <row r="45" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A45" s="30"/>
       <c r="B45" s="28" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D45" s="29">
         <v>4</v>
@@ -4312,10 +4321,10 @@
     <row r="46" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A46" s="35"/>
       <c r="B46" s="28" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D46" s="29">
         <v>4</v>
@@ -4323,7 +4332,7 @@
     </row>
     <row r="47" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A47" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B47" s="37"/>
       <c r="C47" s="38"/>
@@ -4333,13 +4342,13 @@
     </row>
     <row r="48" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A48" s="27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D48" s="29">
         <v>4</v>
@@ -4348,10 +4357,10 @@
     <row r="49" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A49" s="30"/>
       <c r="B49" s="28" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D49" s="29">
         <v>4</v>
@@ -4360,10 +4369,10 @@
     <row r="50" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A50" s="30"/>
       <c r="B50" s="28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D50" s="29">
         <v>4</v>
@@ -4372,10 +4381,10 @@
     <row r="51" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A51" s="30"/>
       <c r="B51" s="28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D51" s="29">
         <v>4</v>
@@ -4384,10 +4393,10 @@
     <row r="52" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A52" s="30"/>
       <c r="B52" s="28" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D52" s="29">
         <v>4</v>
@@ -4396,10 +4405,10 @@
     <row r="53" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A53" s="30"/>
       <c r="B53" s="28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D53" s="29">
         <v>4</v>
@@ -4408,10 +4417,10 @@
     <row r="54" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A54" s="30"/>
       <c r="B54" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D54" s="29">
         <v>4</v>
@@ -4420,10 +4429,10 @@
     <row r="55" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A55" s="30"/>
       <c r="B55" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D55" s="29">
         <v>4</v>
@@ -4432,10 +4441,10 @@
     <row r="56" s="23" customFormat="1" ht="40.5" customHeight="1" spans="1:4">
       <c r="A56" s="30"/>
       <c r="B56" s="28" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D56" s="29">
         <v>4</v>
@@ -4444,10 +4453,10 @@
     <row r="57" s="23" customFormat="1" ht="54" customHeight="1" spans="1:4">
       <c r="A57" s="30"/>
       <c r="B57" s="28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D57" s="29">
         <v>6</v>
@@ -4456,10 +4465,10 @@
     <row r="58" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A58" s="35"/>
       <c r="B58" s="28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D58" s="29">
         <v>6</v>
@@ -4467,7 +4476,7 @@
     </row>
     <row r="59" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A59" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B59" s="37"/>
       <c r="C59" s="38"/>
@@ -4477,13 +4486,13 @@
     </row>
     <row r="60" s="23" customFormat="1" ht="94.5" customHeight="1" spans="1:4">
       <c r="A60" s="27" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D60" s="29">
         <v>32</v>
@@ -4492,10 +4501,10 @@
     <row r="61" s="23" customFormat="1" ht="94.5" customHeight="1" spans="1:4">
       <c r="A61" s="30"/>
       <c r="B61" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D61" s="29">
         <v>32</v>
@@ -4504,10 +4513,10 @@
     <row r="62" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A62" s="35"/>
       <c r="B62" s="28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D62" s="29">
         <v>32</v>
@@ -4515,7 +4524,7 @@
     </row>
     <row r="63" s="23" customFormat="1" ht="13.5" customHeight="1" spans="1:4">
       <c r="A63" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B63" s="37"/>
       <c r="C63" s="38"/>
@@ -4559,13 +4568,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>11</v>
@@ -4573,10 +4582,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C2" s="5">
         <v>32</v>
@@ -4659,10 +4668,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C18" s="5">
         <v>32</v>
@@ -4710,10 +4719,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C27" s="21">
         <v>32</v>
@@ -4786,10 +4795,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C41" s="5">
         <v>32</v>
